--- a/artfynd/A 2787-2024 artfynd.xlsx
+++ b/artfynd/A 2787-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2787-2024 artfynd.xlsx
+++ b/artfynd/A 2787-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99724982</v>
+        <v>99724972</v>
       </c>
       <c r="B2" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400958.990896433</v>
+        <v>400959</v>
       </c>
       <c r="R2" t="n">
-        <v>6206434.737092733</v>
+        <v>6206434</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -810,37 +805,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99724928</v>
+        <v>99725047</v>
       </c>
       <c r="B3" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -869,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400958.990896433</v>
+        <v>400959</v>
       </c>
       <c r="R3" t="n">
-        <v>6206434.737092733</v>
+        <v>6206434</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -945,42 +935,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99725047</v>
+        <v>99724953</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1004,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400958.990896433</v>
+        <v>400959</v>
       </c>
       <c r="R4" t="n">
-        <v>6206434.737092733</v>
+        <v>6206434</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1034,7 +1019,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1044,7 +1029,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1080,15 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99724953</v>
+        <v>99724926</v>
       </c>
       <c r="B5" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,26 +1076,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1139,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>400958.990896433</v>
+        <v>400959</v>
       </c>
       <c r="R5" t="n">
-        <v>6206434.737092733</v>
+        <v>6206434</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 2787-2024 artfynd.xlsx
+++ b/artfynd/A 2787-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Utredning stambana Hässleholm Lund</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99724972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Utredning stambana Hässleholm Lund</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99725047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Utredning stambana Hässleholm Lund</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99724953</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,8 +1212,19 @@
           <t>Utredning stambana Hässleholm Lund</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99724926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>